--- a/artfynd/A 43732-2025 artfynd.xlsx
+++ b/artfynd/A 43732-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129173466</v>
       </c>
       <c r="B2" t="n">
-        <v>57883</v>
+        <v>57885</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>129173376</v>
       </c>
       <c r="B3" t="n">
-        <v>57883</v>
+        <v>57885</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>129173247</v>
       </c>
       <c r="B4" t="n">
-        <v>58093</v>
+        <v>58095</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 43732-2025 artfynd.xlsx
+++ b/artfynd/A 43732-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1022,6 +1022,711 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>129317937</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57738</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100048</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Mindre hackspett</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Dryobates minor</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Skog 1, Stora Orrevattnet, Vg</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>344375</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6435770</v>
+      </c>
+      <c r="S5" t="n">
+        <v>50</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Hålanda</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ropade upprepade gånger, rörde sig något västerut ner mot mossen.</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Ola Freijd</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Ola Freijd</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>129318161</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57722</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Död gran 1, Stora Orrevattnet, Vg</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>344405</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6435753</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Hålanda</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Spår efter födosök.</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Ola Freijd</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Ola Freijd</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>129319575</v>
+      </c>
+      <c r="B7" t="n">
+        <v>5177</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Död gran 3, Stora Orrevattnet, Vg</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>344483</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6435680</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Hålanda</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Ola Freijd</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Ola Freijd</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>129320333</v>
+      </c>
+      <c r="B8" t="n">
+        <v>8439</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Skog 3, Stora Orrevattnet, Vg</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>344406</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6435639</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Hålanda</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Ola Freijd</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Ola Freijd</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>129318064</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57646</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100001</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Duvhök</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Astur gentilis</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Skog 2, Stora Orrevattnet, Vg</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>344375</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6435780</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Hålanda</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>En kort varning, utifrån det lilla hygget alldeles nära norrut.</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Ola Freijd</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Ola Freijd</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>129318005</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57885</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Skog 1, Stora Orrevattnet, Vg</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>344375</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6435770</v>
+      </c>
+      <c r="S10" t="n">
+        <v>50</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Hålanda</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Ola Freijd</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Ola Freijd</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 43732-2025 artfynd.xlsx
+++ b/artfynd/A 43732-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>129173466</v>
       </c>
       <c r="B2" t="n">
-        <v>57885</v>
+        <v>57887</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>129173376</v>
       </c>
       <c r="B3" t="n">
-        <v>57885</v>
+        <v>57887</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>129173247</v>
       </c>
       <c r="B4" t="n">
-        <v>58095</v>
+        <v>58097</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
         <v>129317937</v>
       </c>
       <c r="B5" t="n">
-        <v>57738</v>
+        <v>57740</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>129318161</v>
       </c>
       <c r="B6" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1497,7 +1497,7 @@
         <v>129318064</v>
       </c>
       <c r="B9" t="n">
-        <v>57646</v>
+        <v>57648</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1617,7 +1617,7 @@
         <v>129318005</v>
       </c>
       <c r="B10" t="n">
-        <v>57885</v>
+        <v>57887</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1726,6 +1726,237 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>129320910</v>
+      </c>
+      <c r="B11" t="n">
+        <v>97549</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Skog 7, Stora Orrevattnet, Vg</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>344375</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6435780</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Hålanda</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Ola Freijd</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Ola Freijd</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>129320909</v>
+      </c>
+      <c r="B12" t="n">
+        <v>84962</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>3518</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Smal svampklubba</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Tolypocladium ophioglossoides</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Skog 6, Stora Orrevattnet, Vg</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>344340</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6435637</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Hålanda</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Ola Freijd</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Ola Freijd</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 43732-2025 artfynd.xlsx
+++ b/artfynd/A 43732-2025 artfynd.xlsx
@@ -1732,7 +1732,7 @@
         <v>129320910</v>
       </c>
       <c r="B11" t="n">
-        <v>97549</v>
+        <v>97575</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
         <v>129320909</v>
       </c>
       <c r="B12" t="n">
-        <v>84962</v>
+        <v>84963</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 43732-2025 artfynd.xlsx
+++ b/artfynd/A 43732-2025 artfynd.xlsx
@@ -1732,7 +1732,7 @@
         <v>129320910</v>
       </c>
       <c r="B11" t="n">
-        <v>97575</v>
+        <v>97576</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 43732-2025 artfynd.xlsx
+++ b/artfynd/A 43732-2025 artfynd.xlsx
@@ -1732,7 +1732,7 @@
         <v>129320910</v>
       </c>
       <c r="B11" t="n">
-        <v>97576</v>
+        <v>97577</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 43732-2025 artfynd.xlsx
+++ b/artfynd/A 43732-2025 artfynd.xlsx
@@ -1732,7 +1732,7 @@
         <v>129320910</v>
       </c>
       <c r="B11" t="n">
-        <v>97577</v>
+        <v>97581</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
         <v>129320909</v>
       </c>
       <c r="B12" t="n">
-        <v>84963</v>
+        <v>84968</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 43732-2025 artfynd.xlsx
+++ b/artfynd/A 43732-2025 artfynd.xlsx
@@ -1732,7 +1732,7 @@
         <v>129320910</v>
       </c>
       <c r="B11" t="n">
-        <v>97581</v>
+        <v>97583</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
         <v>129320909</v>
       </c>
       <c r="B12" t="n">
-        <v>84968</v>
+        <v>84970</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 43732-2025 artfynd.xlsx
+++ b/artfynd/A 43732-2025 artfynd.xlsx
@@ -1732,7 +1732,7 @@
         <v>129320910</v>
       </c>
       <c r="B11" t="n">
-        <v>97583</v>
+        <v>97587</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 43732-2025 artfynd.xlsx
+++ b/artfynd/A 43732-2025 artfynd.xlsx
@@ -1732,7 +1732,7 @@
         <v>129320910</v>
       </c>
       <c r="B11" t="n">
-        <v>97587</v>
+        <v>97595</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
         <v>129320909</v>
       </c>
       <c r="B12" t="n">
-        <v>84970</v>
+        <v>84971</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 43732-2025 artfynd.xlsx
+++ b/artfynd/A 43732-2025 artfynd.xlsx
@@ -1732,7 +1732,7 @@
         <v>129320910</v>
       </c>
       <c r="B11" t="n">
-        <v>97595</v>
+        <v>97598</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 43732-2025 artfynd.xlsx
+++ b/artfynd/A 43732-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129173466</v>
       </c>
       <c r="B2" t="n">
-        <v>57887</v>
+        <v>57890</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>129173376</v>
       </c>
       <c r="B3" t="n">
-        <v>57887</v>
+        <v>57890</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>129173247</v>
       </c>
       <c r="B4" t="n">
-        <v>58097</v>
+        <v>58100</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
         <v>129317937</v>
       </c>
       <c r="B5" t="n">
-        <v>57740</v>
+        <v>57743</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>129318161</v>
       </c>
       <c r="B6" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1497,7 +1497,7 @@
         <v>129318064</v>
       </c>
       <c r="B9" t="n">
-        <v>57648</v>
+        <v>57651</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1617,7 +1617,7 @@
         <v>129318005</v>
       </c>
       <c r="B10" t="n">
-        <v>57887</v>
+        <v>57890</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1732,7 +1732,7 @@
         <v>129320910</v>
       </c>
       <c r="B11" t="n">
-        <v>97598</v>
+        <v>97627</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
         <v>129320909</v>
       </c>
       <c r="B12" t="n">
-        <v>84971</v>
+        <v>84998</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 43732-2025 artfynd.xlsx
+++ b/artfynd/A 43732-2025 artfynd.xlsx
@@ -1027,7 +1027,7 @@
         <v>129317937</v>
       </c>
       <c r="B5" t="n">
-        <v>57743</v>
+        <v>57748</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>129318161</v>
       </c>
       <c r="B6" t="n">
-        <v>57727</v>
+        <v>57732</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1497,7 +1497,7 @@
         <v>129318064</v>
       </c>
       <c r="B9" t="n">
-        <v>57651</v>
+        <v>57656</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1617,7 +1617,7 @@
         <v>129318005</v>
       </c>
       <c r="B10" t="n">
-        <v>57890</v>
+        <v>57895</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1732,7 +1732,7 @@
         <v>129320910</v>
       </c>
       <c r="B11" t="n">
-        <v>97627</v>
+        <v>97639</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
         <v>129320909</v>
       </c>
       <c r="B12" t="n">
-        <v>84998</v>
+        <v>85004</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 43732-2025 artfynd.xlsx
+++ b/artfynd/A 43732-2025 artfynd.xlsx
@@ -1027,7 +1027,7 @@
         <v>129317937</v>
       </c>
       <c r="B5" t="n">
-        <v>57748</v>
+        <v>57749</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>129318161</v>
       </c>
       <c r="B6" t="n">
-        <v>57732</v>
+        <v>57733</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1497,7 +1497,7 @@
         <v>129318064</v>
       </c>
       <c r="B9" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1617,7 +1617,7 @@
         <v>129318005</v>
       </c>
       <c r="B10" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1732,7 +1732,7 @@
         <v>129320910</v>
       </c>
       <c r="B11" t="n">
-        <v>97639</v>
+        <v>97640</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
         <v>129320909</v>
       </c>
       <c r="B12" t="n">
-        <v>85004</v>
+        <v>85005</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 43732-2025 artfynd.xlsx
+++ b/artfynd/A 43732-2025 artfynd.xlsx
@@ -1732,7 +1732,7 @@
         <v>129320910</v>
       </c>
       <c r="B11" t="n">
-        <v>97640</v>
+        <v>97645</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
         <v>129320909</v>
       </c>
       <c r="B12" t="n">
-        <v>85005</v>
+        <v>85010</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
